--- a/artfynd/A 88-2024 artfynd.xlsx
+++ b/artfynd/A 88-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118350217</v>
+        <v>118350126</v>
       </c>
       <c r="B2" t="n">
-        <v>105495</v>
+        <v>101185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679359</v>
+        <v>679310</v>
       </c>
       <c r="R2" t="n">
-        <v>6644492</v>
+        <v>6644507</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vuxen, grov ask.</t>
+          <t>I sydvänd torrbacke mot åkern. Två bestånd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118350126</v>
+        <v>118350217</v>
       </c>
       <c r="B3" t="n">
-        <v>101185</v>
+        <v>105495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679310</v>
+        <v>679359</v>
       </c>
       <c r="R3" t="n">
-        <v>6644507</v>
+        <v>6644492</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I sydvänd torrbacke mot åkern. Två bestånd.</t>
+          <t>Vuxen, grov ask.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 88-2024 artfynd.xlsx
+++ b/artfynd/A 88-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118350126</v>
       </c>
       <c r="B2" t="n">
-        <v>101185</v>
+        <v>101192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>118350217</v>
       </c>
       <c r="B3" t="n">
-        <v>105495</v>
+        <v>105502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 88-2024 artfynd.xlsx
+++ b/artfynd/A 88-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118350126</v>
+        <v>118350217</v>
       </c>
       <c r="B2" t="n">
-        <v>101192</v>
+        <v>105502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679310</v>
+        <v>679359</v>
       </c>
       <c r="R2" t="n">
-        <v>6644507</v>
+        <v>6644492</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I sydvänd torrbacke mot åkern. Två bestånd.</t>
+          <t>Vuxen, grov ask.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118350217</v>
+        <v>118350126</v>
       </c>
       <c r="B3" t="n">
-        <v>105502</v>
+        <v>101192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679359</v>
+        <v>679310</v>
       </c>
       <c r="R3" t="n">
-        <v>6644492</v>
+        <v>6644507</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vuxen, grov ask.</t>
+          <t>I sydvänd torrbacke mot åkern. Två bestånd.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 88-2024 artfynd.xlsx
+++ b/artfynd/A 88-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118350217</v>
+        <v>118351350</v>
       </c>
       <c r="B2" t="n">
-        <v>105502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hushagsbacken (Hushagsbacken), Upl</t>
+          <t>Hushagsbacken, Hushagsbacken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679359</v>
+        <v>679330</v>
       </c>
       <c r="R2" t="n">
-        <v>6644492</v>
+        <v>6644490</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vuxen, grov ask.</t>
+          <t>På grov solbelyst vårtbjörk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,53 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118350126</v>
+        <v>118350217</v>
       </c>
       <c r="B3" t="n">
-        <v>101192</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hushagsbacken (Hushagsbacken), Upl</t>
+          <t>Hushagsbacken, Hushagsbacken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679310</v>
+        <v>679359</v>
       </c>
       <c r="R3" t="n">
-        <v>6644507</v>
+        <v>6644492</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I sydvänd torrbacke mot åkern. Två bestånd.</t>
+          <t>Vuxen, grov ask.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +896,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118350126</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hushagsbacken, Hushagsbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679310</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6644507</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I sydvänd torrbacke mot åkern. Två bestånd.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
